--- a/public/volunteer-roster/templates/sausage-sizzle-roster.xlsx
+++ b/public/volunteer-roster/templates/sausage-sizzle-roster.xlsx
@@ -75,8 +75,8 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -98,7 +98,7 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Four people a shift is the workable minimum: two cooking, one on bread and onions, one on money. Rotate whoever is on the barbecue — it is the hot job.</t>
+          <t xml:space="preserve">12 to 14 people plus a coordinator covers a full day, weighted to the middle. A hardware car park fills from about 10.30am, so overstaff the shift starting at 10 — not the one at 8.</t>
         </is>
       </c>
       <c r="B2" s="0"/>
@@ -118,12 +118,12 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shift</t>
+          <t xml:space="preserve">When</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Time</t>
+          <t xml:space="preserve">Slot</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
@@ -150,17 +150,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shift 1</t>
+          <t xml:space="preserve">All day</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8:00am – 10:00am</t>
+          <t xml:space="preserve">BBQ Captain</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooking</t>
+          <t xml:space="preserve">7.30am – 5pm. Not rostered on the grill</t>
         </is>
       </c>
       <c r="D5" s="2"/>
@@ -168,23 +168,31 @@
       <c r="F5" s="2"/>
     </row>
     <row r="6">
-      <c r="A6" s="0"/>
-      <c r="B6" s="0"/>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cooking</t>
-        </is>
-      </c>
-      <c r="D6" s="0"/>
-      <c r="E6" s="0"/>
-      <c r="F6" s="0"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7.30 – 8am</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bump-in</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unload and gazebo</t>
+        </is>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="0"/>
       <c r="B7" s="0"/>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bread, onions and sauce</t>
+          <t xml:space="preserve">Sandbags</t>
         </is>
       </c>
       <c r="D7" s="0"/>
@@ -196,7 +204,7 @@
       <c r="B8" s="0"/>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Money and orders</t>
+          <t xml:space="preserve">Plate hot, onions on</t>
         </is>
       </c>
       <c r="D8" s="0"/>
@@ -204,43 +212,43 @@
       <c r="F8" s="0"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shift 2</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10:00am – 12:00pm</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cooking</t>
-        </is>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="A9" s="0"/>
+      <c r="B9" s="0"/>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stock and float</t>
+        </is>
+      </c>
+      <c r="D9" s="0"/>
+      <c r="E9" s="0"/>
+      <c r="F9" s="0"/>
     </row>
     <row r="10">
-      <c r="A10" s="0"/>
-      <c r="B10" s="0"/>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cooking</t>
-        </is>
-      </c>
-      <c r="D10" s="0"/>
-      <c r="E10" s="0"/>
-      <c r="F10" s="0"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 – 10am</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shift 1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cook (18+)</t>
+        </is>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="0"/>
       <c r="B11" s="0"/>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bread, onions and sauce</t>
+          <t xml:space="preserve">Bread and onions</t>
         </is>
       </c>
       <c r="D11" s="0"/>
@@ -252,7 +260,7 @@
       <c r="B12" s="0"/>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Money and orders</t>
+          <t xml:space="preserve">Money</t>
         </is>
       </c>
       <c r="D12" s="0"/>
@@ -262,17 +270,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shift 3</t>
+          <t xml:space="preserve">10am – 12pm</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12:00pm – 2:00pm</t>
+          <t xml:space="preserve">Shift 2 — peak starts here</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooking</t>
+          <t xml:space="preserve">Cook (18+)</t>
         </is>
       </c>
       <c r="D13" s="2"/>
@@ -284,7 +292,7 @@
       <c r="B14" s="0"/>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooking</t>
+          <t xml:space="preserve">Cook (18+)</t>
         </is>
       </c>
       <c r="D14" s="0"/>
@@ -296,7 +304,7 @@
       <c r="B15" s="0"/>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bread, onions and sauce</t>
+          <t xml:space="preserve">Bread and serving</t>
         </is>
       </c>
       <c r="D15" s="0"/>
@@ -308,7 +316,7 @@
       <c r="B16" s="0"/>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Money and orders</t>
+          <t xml:space="preserve">Bread and serving</t>
         </is>
       </c>
       <c r="D16" s="0"/>
@@ -316,43 +324,43 @@
       <c r="F16" s="0"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Shift 4</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2:00pm – 4:00pm</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cooking</t>
-        </is>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="A17" s="0"/>
+      <c r="B17" s="0"/>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Money</t>
+        </is>
+      </c>
+      <c r="D17" s="0"/>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0"/>
     </row>
     <row r="18">
-      <c r="A18" s="0"/>
-      <c r="B18" s="0"/>
-      <c r="C18" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cooking</t>
-        </is>
-      </c>
-      <c r="D18" s="0"/>
-      <c r="E18" s="0"/>
-      <c r="F18" s="0"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 – 2pm</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shift 3</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cook (18+)</t>
+        </is>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" s="0"/>
       <c r="B19" s="0"/>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bread, onions and sauce</t>
+          <t xml:space="preserve">Cook (18+)</t>
         </is>
       </c>
       <c r="D19" s="0"/>
@@ -364,7 +372,7 @@
       <c r="B20" s="0"/>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Money and orders</t>
+          <t xml:space="preserve">Bread and serving</t>
         </is>
       </c>
       <c r="D20" s="0"/>
@@ -372,31 +380,23 @@
       <c r="F20" s="0"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Set-up</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7:15am – 8:00am</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Barbecue and gas</t>
-        </is>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
+      <c r="A21" s="0"/>
+      <c r="B21" s="0"/>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bread and serving</t>
+        </is>
+      </c>
+      <c r="D21" s="0"/>
+      <c r="E21" s="0"/>
+      <c r="F21" s="0"/>
     </row>
     <row r="22">
       <c r="A22" s="0"/>
       <c r="B22" s="0"/>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esky, stock and float</t>
+          <t xml:space="preserve">Money</t>
         </is>
       </c>
       <c r="D22" s="0"/>
@@ -406,17 +406,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pack-down</t>
+          <t xml:space="preserve">2 – 4pm</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4:00pm – 5:00pm</t>
+          <t xml:space="preserve">Shift 4</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clean barbecue</t>
+          <t xml:space="preserve">Cook (18+)</t>
         </is>
       </c>
       <c r="D23" s="2"/>
@@ -428,7 +428,7 @@
       <c r="B24" s="0"/>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rubbish and leftovers</t>
+          <t xml:space="preserve">Bread</t>
         </is>
       </c>
       <c r="D24" s="0"/>
@@ -438,22 +438,110 @@
     <row r="25">
       <c r="A25" s="0"/>
       <c r="B25" s="0"/>
-      <c r="C25" s="0"/>
+      <c r="C25" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Money and drinks</t>
+        </is>
+      </c>
       <c r="D25" s="0"/>
       <c r="E25" s="0"/>
       <c r="F25" s="0"/>
     </row>
     <row r="26">
-      <c r="A26" s="0" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10am – 3pm</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Restock runner</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Has a car. Ice, stock, emergency bread run</t>
+        </is>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 – 5pm</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pack-down</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Degrease the pad</t>
+        </is>
+      </c>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="0"/>
+      <c r="B28" s="0"/>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bag rubbish</t>
+        </is>
+      </c>
+      <c r="D28" s="0"/>
+      <c r="E28" s="0"/>
+      <c r="F28" s="0"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="0"/>
+      <c r="B29" s="0"/>
+      <c r="C29" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cash up</t>
+        </is>
+      </c>
+      <c r="D29" s="0"/>
+      <c r="E29" s="0"/>
+      <c r="F29" s="0"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="0"/>
+      <c r="B30" s="0"/>
+      <c r="C30" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Load out</t>
+        </is>
+      </c>
+      <c r="D30" s="0"/>
+      <c r="E30" s="0"/>
+      <c r="F30" s="0"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="0"/>
+      <c r="B31" s="0"/>
+      <c r="C31" s="0"/>
+      <c r="D31" s="0"/>
+      <c r="E31" s="0"/>
+      <c r="F31" s="0"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">Made with bitibybit.com/volunteer-roster/ — free, no accounts.</t>
         </is>
       </c>
-      <c r="B26" s="0"/>
-      <c r="C26" s="0"/>
-      <c r="D26" s="0"/>
-      <c r="E26" s="0"/>
-      <c r="F26" s="0"/>
+      <c r="B32" s="0"/>
+      <c r="C32" s="0"/>
+      <c r="D32" s="0"/>
+      <c r="E32" s="0"/>
+      <c r="F32" s="0"/>
     </row>
   </sheetData>
 </worksheet>
